--- a/data/availability/projects/marakez/district-5.xlsx
+++ b/data/availability/projects/marakez/district-5.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for district-5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1047,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1097,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1104,7 +1114,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1137,7 +1147,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1154,7 +1164,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1187,7 +1197,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1309,7 +1319,6 @@
       <c r="G2" t="n">
         <v>224</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1320,7 +1329,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1366,7 +1375,6 @@
       <c r="G3" t="n">
         <v>224</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1377,7 +1385,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1423,7 +1431,6 @@
       <c r="G4" t="n">
         <v>224</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1434,7 +1441,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1480,7 +1487,6 @@
       <c r="G5" t="n">
         <v>224</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1491,7 +1497,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1537,7 +1543,6 @@
       <c r="G6" t="n">
         <v>224</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1548,7 +1553,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1594,7 +1599,6 @@
       <c r="G7" t="n">
         <v>224</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1666,7 +1670,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1712,7 +1716,6 @@
       <c r="G9" t="n">
         <v>149</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1723,7 +1726,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1769,7 +1772,6 @@
       <c r="G10" t="n">
         <v>343</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1780,7 +1782,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1826,7 +1828,6 @@
       <c r="G11" t="n">
         <v>322</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1837,7 +1838,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1883,7 +1884,6 @@
       <c r="G12" t="n">
         <v>102</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1940,7 +1940,6 @@
       <c r="G13" t="n">
         <v>224</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -1951,7 +1950,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1997,7 +1996,6 @@
       <c r="G14" t="n">
         <v>191</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2008,7 +2006,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2054,7 +2052,6 @@
       <c r="G15" t="n">
         <v>136</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2065,7 +2062,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2111,7 +2108,6 @@
       <c r="G16" t="n">
         <v>343</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2122,7 +2118,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2183,7 +2179,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2229,7 +2225,6 @@
       <c r="G18" t="n">
         <v>126</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2240,7 +2235,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2286,7 +2281,6 @@
       <c r="G19" t="n">
         <v>131</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2297,7 +2291,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2358,7 +2352,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2404,7 +2398,6 @@
       <c r="G21" t="n">
         <v>154</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2415,7 +2408,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2461,7 +2454,6 @@
       <c r="G22" t="n">
         <v>210</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2472,7 +2464,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2533,7 +2525,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2579,7 +2571,6 @@
       <c r="G24" t="n">
         <v>130</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2590,7 +2581,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2636,7 +2627,6 @@
       <c r="G25" t="n">
         <v>136</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2647,7 +2637,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2693,7 +2683,6 @@
       <c r="G26" t="n">
         <v>224</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2704,7 +2693,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2750,7 +2739,6 @@
       <c r="G27" t="n">
         <v>81</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2761,7 +2749,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2807,7 +2795,6 @@
       <c r="G28" t="n">
         <v>144</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2818,7 +2805,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2864,7 +2851,6 @@
       <c r="G29" t="n">
         <v>218</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2875,7 +2861,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2921,7 +2907,6 @@
       <c r="G30" t="n">
         <v>154</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2932,7 +2917,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2978,7 +2963,6 @@
       <c r="G31" t="n">
         <v>188</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -2989,7 +2973,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3035,7 +3019,6 @@
       <c r="G32" t="n">
         <v>164</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3046,7 +3029,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3092,7 +3075,6 @@
       <c r="G33" t="n">
         <v>188</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3103,7 +3085,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3149,7 +3131,6 @@
       <c r="G34" t="n">
         <v>191</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3160,7 +3141,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3206,7 +3187,6 @@
       <c r="G35" t="n">
         <v>136</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3217,7 +3197,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3278,7 +3258,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3324,7 +3304,6 @@
       <c r="G37" t="n">
         <v>164</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3335,7 +3314,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3381,7 +3360,6 @@
       <c r="G38" t="n">
         <v>164</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3392,7 +3370,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3438,7 +3416,6 @@
       <c r="G39" t="n">
         <v>163</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3449,7 +3426,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3495,7 +3472,6 @@
       <c r="G40" t="n">
         <v>211</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3506,7 +3482,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3552,7 +3528,6 @@
       <c r="G41" t="n">
         <v>144</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3563,7 +3538,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3609,7 +3584,6 @@
       <c r="G42" t="n">
         <v>144</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3620,7 +3594,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3666,7 +3640,6 @@
       <c r="G43" t="n">
         <v>200</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3677,7 +3650,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3723,7 +3696,6 @@
       <c r="G44" t="n">
         <v>144</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3734,7 +3706,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3780,7 +3752,6 @@
       <c r="G45" t="n">
         <v>82</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3791,7 +3762,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3837,7 +3808,6 @@
       <c r="G46" t="n">
         <v>131</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3848,7 +3818,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3909,7 +3879,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3955,7 +3925,6 @@
       <c r="G48" t="n">
         <v>136</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -3966,7 +3935,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4012,7 +3981,6 @@
       <c r="G49" t="n">
         <v>136</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4023,7 +3991,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4069,7 +4037,6 @@
       <c r="G50" t="n">
         <v>136</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4080,7 +4047,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4126,7 +4093,6 @@
       <c r="G51" t="n">
         <v>136</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4137,7 +4103,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4183,7 +4149,6 @@
       <c r="G52" t="n">
         <v>136</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4194,7 +4159,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4240,7 +4205,6 @@
       <c r="G53" t="n">
         <v>134</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4251,7 +4215,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4273,7 +4237,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4297,7 +4261,6 @@
       <c r="G54" t="n">
         <v>183</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4308,7 +4271,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4330,7 +4293,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4354,7 +4317,6 @@
       <c r="G55" t="n">
         <v>188</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4365,7 +4327,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4387,7 +4349,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4411,7 +4373,6 @@
       <c r="G56" t="n">
         <v>156</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4422,7 +4383,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4444,7 +4405,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4468,7 +4429,6 @@
       <c r="G57" t="n">
         <v>101</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4479,7 +4439,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4501,7 +4461,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4525,7 +4485,6 @@
       <c r="G58" t="n">
         <v>138</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape &amp; Amenities</t>
@@ -4536,7 +4495,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
